--- a/data/Delta.xlsx
+++ b/data/Delta.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\OneDrive - kanggle\XMU\likangguo\other\github\zhuhai_omicron\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BE16DD06-19B5-4533-AE63-D209F9B0DBDE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EFC500F9-9159-42A2-803C-D34C30B41731}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -55,10 +55,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>datereport</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>vaccine</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -706,6 +702,10 @@
   </si>
   <si>
     <t>O</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>datereported</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -1218,7 +1218,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="C1" s="2" t="s">
         <v>1</v>
@@ -1227,40 +1227,40 @@
         <v>2</v>
       </c>
       <c r="E1" t="s">
+        <v>169</v>
+      </c>
+      <c r="F1" t="s">
         <v>170</v>
       </c>
-      <c r="F1" t="s">
-        <v>171</v>
-      </c>
       <c r="G1" s="6" t="s">
+        <v>163</v>
+      </c>
+      <c r="H1" s="6" t="s">
         <v>164</v>
       </c>
-      <c r="H1" s="6" t="s">
-        <v>165</v>
-      </c>
       <c r="I1" s="4" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J1" s="5" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="K1" s="5" t="s">
+        <v>199</v>
+      </c>
+      <c r="L1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="M1" s="1" t="s">
+        <v>168</v>
+      </c>
+      <c r="N1" s="11" t="s">
         <v>4</v>
       </c>
-      <c r="M1" s="1" t="s">
-        <v>169</v>
-      </c>
-      <c r="N1" s="11" t="s">
-        <v>5</v>
-      </c>
       <c r="O1" t="s">
+        <v>191</v>
+      </c>
+      <c r="P1" t="s">
         <v>192</v>
-      </c>
-      <c r="P1" t="s">
-        <v>193</v>
       </c>
     </row>
     <row r="2" spans="1:16" x14ac:dyDescent="0.2">
@@ -1268,19 +1268,19 @@
         <v>9</v>
       </c>
       <c r="B2" s="28" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="C2">
         <v>65</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E2" s="3" t="s">
+        <v>180</v>
+      </c>
+      <c r="F2" s="3" t="s">
         <v>181</v>
-      </c>
-      <c r="F2" s="3" t="s">
-        <v>182</v>
       </c>
       <c r="G2" s="8">
         <v>44400</v>
@@ -1318,19 +1318,19 @@
         <v>17</v>
       </c>
       <c r="B3" s="28" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="C3">
         <v>36</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E3" s="3" t="s">
+        <v>175</v>
+      </c>
+      <c r="F3" s="3" t="s">
         <v>176</v>
-      </c>
-      <c r="F3" s="3" t="s">
-        <v>177</v>
       </c>
       <c r="G3" s="8">
         <v>44401</v>
@@ -1368,19 +1368,19 @@
         <v>40</v>
       </c>
       <c r="B4" s="28" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="C4">
         <v>34</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="G4" s="8">
         <v>44402</v>
@@ -1401,7 +1401,7 @@
         <v>1</v>
       </c>
       <c r="M4" s="9" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="N4" s="8">
         <v>44404</v>
@@ -1412,19 +1412,19 @@
         <v>47</v>
       </c>
       <c r="B5" s="28" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="C5">
         <v>59</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E5" s="3" t="s">
+        <v>182</v>
+      </c>
+      <c r="F5" s="3" t="s">
         <v>183</v>
-      </c>
-      <c r="F5" s="3" t="s">
-        <v>184</v>
       </c>
       <c r="G5" s="8">
         <v>44401</v>
@@ -1445,7 +1445,7 @@
         <v>1</v>
       </c>
       <c r="M5" s="9" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="N5" s="8">
         <v>44403</v>
@@ -1456,19 +1456,19 @@
         <v>3</v>
       </c>
       <c r="B6" s="28" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="C6">
         <v>38</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E6" s="3" t="s">
+        <v>175</v>
+      </c>
+      <c r="F6" s="3" t="s">
         <v>176</v>
-      </c>
-      <c r="F6" s="3" t="s">
-        <v>177</v>
       </c>
       <c r="G6" s="8">
         <v>44399</v>
@@ -1489,7 +1489,7 @@
         <v>1</v>
       </c>
       <c r="M6" s="9" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="N6" s="8">
         <v>44399</v>
@@ -1500,19 +1500,19 @@
         <v>83</v>
       </c>
       <c r="B7" s="28" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="C7">
         <v>28</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E7" s="3" t="s">
+        <v>175</v>
+      </c>
+      <c r="F7" s="3" t="s">
         <v>176</v>
-      </c>
-      <c r="F7" s="3" t="s">
-        <v>177</v>
       </c>
       <c r="G7" s="8">
         <v>44405</v>
@@ -1533,7 +1533,7 @@
         <v>0</v>
       </c>
       <c r="M7" s="7" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="N7" s="8">
         <v>44405</v>
@@ -1552,19 +1552,19 @@
         <v>94</v>
       </c>
       <c r="B8" s="28" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="C8">
         <v>39</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E8" s="3" t="s">
+        <v>175</v>
+      </c>
+      <c r="F8" s="3" t="s">
         <v>176</v>
-      </c>
-      <c r="F8" s="3" t="s">
-        <v>177</v>
       </c>
       <c r="G8" s="8"/>
       <c r="H8" s="8"/>
@@ -1581,7 +1581,7 @@
         <v>0</v>
       </c>
       <c r="M8" s="7" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="N8" s="8">
         <v>44404</v>
@@ -1600,19 +1600,19 @@
         <v>73</v>
       </c>
       <c r="B9" s="28" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="C9">
         <v>47</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="G9" s="8">
         <v>44404</v>
@@ -1633,7 +1633,7 @@
         <v>1</v>
       </c>
       <c r="M9" s="9" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="N9" s="8">
         <v>44399</v>
@@ -1652,19 +1652,19 @@
         <v>118</v>
       </c>
       <c r="B10" s="28" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="C10">
         <v>22</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E10" s="3" t="s">
+        <v>175</v>
+      </c>
+      <c r="F10" s="3" t="s">
         <v>176</v>
-      </c>
-      <c r="F10" s="3" t="s">
-        <v>177</v>
       </c>
       <c r="G10" s="8"/>
       <c r="H10" s="8"/>
@@ -1681,7 +1681,7 @@
         <v>1</v>
       </c>
       <c r="M10" s="7" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="N10" s="8">
         <v>44405</v>
@@ -1700,19 +1700,19 @@
         <v>120</v>
       </c>
       <c r="B11" s="28" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="C11">
         <v>59</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E11" s="3" t="s">
+        <v>175</v>
+      </c>
+      <c r="F11" s="3" t="s">
         <v>176</v>
-      </c>
-      <c r="F11" s="3" t="s">
-        <v>177</v>
       </c>
       <c r="G11" s="8"/>
       <c r="H11" s="8"/>
@@ -1729,7 +1729,7 @@
         <v>1</v>
       </c>
       <c r="M11" s="7" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="N11" s="8">
         <v>44405</v>
@@ -1748,19 +1748,19 @@
         <v>54</v>
       </c>
       <c r="B12" s="28" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="C12">
         <v>53</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E12" s="3" t="s">
+        <v>180</v>
+      </c>
+      <c r="F12" s="3" t="s">
         <v>181</v>
-      </c>
-      <c r="F12" s="3" t="s">
-        <v>182</v>
       </c>
       <c r="G12" s="8">
         <v>44401</v>
@@ -1781,7 +1781,7 @@
         <v>2</v>
       </c>
       <c r="M12" s="9" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="N12" s="8">
         <v>44397</v>
@@ -1800,19 +1800,19 @@
         <v>11</v>
       </c>
       <c r="B13" s="28" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="C13">
         <v>29</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E13" s="3" t="s">
+        <v>178</v>
+      </c>
+      <c r="F13" s="3" t="s">
         <v>179</v>
-      </c>
-      <c r="F13" s="3" t="s">
-        <v>180</v>
       </c>
       <c r="G13" s="8">
         <v>44401</v>
@@ -1833,7 +1833,7 @@
         <v>1</v>
       </c>
       <c r="M13" s="7" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="N13" s="8">
         <v>44392</v>
@@ -1852,19 +1852,19 @@
         <v>12</v>
       </c>
       <c r="B14" s="28" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="C14">
         <v>40</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E14" s="3" t="s">
+        <v>182</v>
+      </c>
+      <c r="F14" s="3" t="s">
         <v>183</v>
-      </c>
-      <c r="F14" s="3" t="s">
-        <v>184</v>
       </c>
       <c r="G14" s="8">
         <v>44401</v>
@@ -1885,7 +1885,7 @@
         <v>1</v>
       </c>
       <c r="M14" s="7" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="N14" s="8">
         <v>44390</v>
@@ -1896,19 +1896,19 @@
         <v>107</v>
       </c>
       <c r="B15" s="28" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="C15">
         <v>47</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E15" s="3" t="s">
+        <v>175</v>
+      </c>
+      <c r="F15" s="3" t="s">
         <v>176</v>
-      </c>
-      <c r="F15" s="3" t="s">
-        <v>177</v>
       </c>
       <c r="G15" s="8"/>
       <c r="H15" s="8"/>
@@ -1925,7 +1925,7 @@
         <v>2</v>
       </c>
       <c r="M15" s="9" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="N15" s="8">
         <v>44399</v>
@@ -1944,19 +1944,19 @@
         <v>69</v>
       </c>
       <c r="B16" s="28" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="C16">
         <v>44</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E16" s="3" t="s">
+        <v>178</v>
+      </c>
+      <c r="F16" s="3" t="s">
         <v>179</v>
-      </c>
-      <c r="F16" s="3" t="s">
-        <v>180</v>
       </c>
       <c r="G16" s="8">
         <v>44405</v>
@@ -1977,7 +1977,7 @@
         <v>1</v>
       </c>
       <c r="M16" s="7" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="N16" s="8">
         <v>44394</v>
@@ -1996,19 +1996,19 @@
         <v>46</v>
       </c>
       <c r="B17" s="28" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="C17">
         <v>18</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="F17" s="3" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="G17" s="8">
         <v>44405</v>
@@ -2046,19 +2046,19 @@
         <v>67</v>
       </c>
       <c r="B18" s="28" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="C18">
         <v>31</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E18" s="3" t="s">
+        <v>178</v>
+      </c>
+      <c r="F18" s="3" t="s">
         <v>179</v>
-      </c>
-      <c r="F18" s="3" t="s">
-        <v>180</v>
       </c>
       <c r="G18" s="8">
         <v>44402</v>
@@ -2079,7 +2079,7 @@
         <v>1</v>
       </c>
       <c r="M18" s="7" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="N18" s="8">
         <v>44392</v>
@@ -2098,19 +2098,19 @@
         <v>79</v>
       </c>
       <c r="B19" s="28" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="C19">
         <v>58</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E19" s="3" t="s">
+        <v>175</v>
+      </c>
+      <c r="F19" s="3" t="s">
         <v>176</v>
-      </c>
-      <c r="F19" s="3" t="s">
-        <v>177</v>
       </c>
       <c r="G19" s="8">
         <v>44405</v>
@@ -2131,7 +2131,7 @@
         <v>1</v>
       </c>
       <c r="M19" s="7" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="N19" s="8">
         <v>44390</v>
@@ -2150,19 +2150,19 @@
         <v>77</v>
       </c>
       <c r="B20" s="28" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="C20">
         <v>22</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E20" s="3" t="s">
+        <v>175</v>
+      </c>
+      <c r="F20" s="3" t="s">
         <v>176</v>
-      </c>
-      <c r="F20" s="3" t="s">
-        <v>177</v>
       </c>
       <c r="G20" s="8">
         <v>44404</v>
@@ -2183,7 +2183,7 @@
         <v>1</v>
       </c>
       <c r="M20" s="7" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="N20" s="8">
         <v>44389</v>
@@ -2202,19 +2202,19 @@
         <v>36</v>
       </c>
       <c r="B21" s="28" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="C21">
         <v>43</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E21" s="3" t="s">
+        <v>175</v>
+      </c>
+      <c r="F21" s="3" t="s">
         <v>176</v>
-      </c>
-      <c r="F21" s="3" t="s">
-        <v>177</v>
       </c>
       <c r="G21" s="8">
         <v>44401</v>
@@ -2235,7 +2235,7 @@
         <v>1</v>
       </c>
       <c r="M21" s="7" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="N21" s="8">
         <v>44384</v>
@@ -2246,19 +2246,19 @@
         <v>57</v>
       </c>
       <c r="B22" s="28" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="C22">
         <v>49</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E22" s="3" t="s">
+        <v>175</v>
+      </c>
+      <c r="F22" s="3" t="s">
         <v>176</v>
-      </c>
-      <c r="F22" s="3" t="s">
-        <v>177</v>
       </c>
       <c r="G22" s="8">
         <v>44397</v>
@@ -2279,7 +2279,7 @@
         <v>1</v>
       </c>
       <c r="M22" s="7" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="N22" s="8">
         <v>44385</v>
@@ -2290,19 +2290,19 @@
         <v>51</v>
       </c>
       <c r="B23" s="28" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="C23">
         <v>30</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E23" s="3" t="s">
+        <v>175</v>
+      </c>
+      <c r="F23" s="3" t="s">
         <v>176</v>
-      </c>
-      <c r="F23" s="3" t="s">
-        <v>177</v>
       </c>
       <c r="G23" s="8">
         <v>44404</v>
@@ -2323,7 +2323,7 @@
         <v>1</v>
       </c>
       <c r="M23" s="7" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="N23" s="8">
         <v>44384</v>
@@ -2342,19 +2342,19 @@
         <v>116</v>
       </c>
       <c r="B24" s="28" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="C24">
         <v>63</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E24" s="3" t="s">
+        <v>175</v>
+      </c>
+      <c r="F24" s="3" t="s">
         <v>176</v>
-      </c>
-      <c r="F24" s="3" t="s">
-        <v>177</v>
       </c>
       <c r="G24" s="8"/>
       <c r="H24" s="8"/>
@@ -2371,7 +2371,7 @@
         <v>1</v>
       </c>
       <c r="M24" s="7" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="N24" s="8">
         <v>44390</v>
@@ -2390,19 +2390,19 @@
         <v>82</v>
       </c>
       <c r="B25" s="28" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="C25">
         <v>18</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E25" s="3" t="s">
+        <v>175</v>
+      </c>
+      <c r="F25" s="3" t="s">
         <v>176</v>
-      </c>
-      <c r="F25" s="3" t="s">
-        <v>177</v>
       </c>
       <c r="G25" s="8">
         <v>44401</v>
@@ -2440,19 +2440,19 @@
         <v>25</v>
       </c>
       <c r="B26" s="28" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="C26">
         <v>36</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E26" s="3" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="F26" s="3" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="G26" s="8">
         <v>44402</v>
@@ -2473,7 +2473,7 @@
         <v>1</v>
       </c>
       <c r="M26" s="7" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="N26" s="8">
         <v>44379</v>
@@ -2484,19 +2484,19 @@
         <v>15</v>
       </c>
       <c r="B27" s="28" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="C27">
         <v>34</v>
       </c>
       <c r="D27" s="3" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E27" s="3" t="s">
+        <v>173</v>
+      </c>
+      <c r="F27" s="3" t="s">
         <v>174</v>
-      </c>
-      <c r="F27" s="3" t="s">
-        <v>175</v>
       </c>
       <c r="G27" s="8">
         <v>44401</v>
@@ -2517,7 +2517,7 @@
         <v>1</v>
       </c>
       <c r="M27" s="7" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="N27" s="8">
         <v>44378</v>
@@ -2528,19 +2528,19 @@
         <v>117</v>
       </c>
       <c r="B28" s="28" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="C28">
         <v>31</v>
       </c>
       <c r="D28" s="3" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E28" s="3" t="s">
+        <v>175</v>
+      </c>
+      <c r="F28" s="3" t="s">
         <v>176</v>
-      </c>
-      <c r="F28" s="3" t="s">
-        <v>177</v>
       </c>
       <c r="G28" s="8"/>
       <c r="H28" s="8"/>
@@ -2557,7 +2557,7 @@
         <v>1</v>
       </c>
       <c r="M28" s="7" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="N28" s="8">
         <v>44384</v>
@@ -2576,19 +2576,19 @@
         <v>87</v>
       </c>
       <c r="B29" s="28" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="C29">
         <v>39</v>
       </c>
       <c r="D29" s="3" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E29" s="3" t="s">
+        <v>175</v>
+      </c>
+      <c r="F29" s="3" t="s">
         <v>176</v>
-      </c>
-      <c r="F29" s="3" t="s">
-        <v>177</v>
       </c>
       <c r="G29" s="8">
         <v>44406</v>
@@ -2609,7 +2609,7 @@
         <v>1</v>
       </c>
       <c r="M29" s="7" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="N29" s="8">
         <v>44379</v>
@@ -2628,19 +2628,19 @@
         <v>6</v>
       </c>
       <c r="B30" s="28" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="C30">
         <v>39</v>
       </c>
       <c r="D30" s="3" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E30" s="3" t="s">
+        <v>178</v>
+      </c>
+      <c r="F30" s="3" t="s">
         <v>179</v>
-      </c>
-      <c r="F30" s="3" t="s">
-        <v>180</v>
       </c>
       <c r="G30" s="8">
         <v>44401</v>
@@ -2661,7 +2661,7 @@
         <v>2</v>
       </c>
       <c r="M30" s="9" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="N30" s="8">
         <v>44371</v>
@@ -2680,19 +2680,19 @@
         <v>121</v>
       </c>
       <c r="B31" s="28" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="C31">
         <v>26</v>
       </c>
       <c r="D31" s="3" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E31" s="3" t="s">
+        <v>175</v>
+      </c>
+      <c r="F31" s="3" t="s">
         <v>176</v>
-      </c>
-      <c r="F31" s="3" t="s">
-        <v>177</v>
       </c>
       <c r="G31" s="8"/>
       <c r="H31" s="8"/>
@@ -2709,7 +2709,7 @@
         <v>1</v>
       </c>
       <c r="M31" s="7" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="N31" s="8">
         <v>44383</v>
@@ -2728,19 +2728,19 @@
         <v>113</v>
       </c>
       <c r="B32" s="28" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="C32">
         <v>48</v>
       </c>
       <c r="D32" s="3" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E32" s="3" t="s">
+        <v>175</v>
+      </c>
+      <c r="F32" s="3" t="s">
         <v>176</v>
-      </c>
-      <c r="F32" s="3" t="s">
-        <v>177</v>
       </c>
       <c r="G32" s="8"/>
       <c r="H32" s="8"/>
@@ -2757,7 +2757,7 @@
         <v>1</v>
       </c>
       <c r="M32" s="7" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="N32" s="8">
         <v>44382</v>
@@ -2780,7 +2780,7 @@
         <v>54</v>
       </c>
       <c r="D33" s="3" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E33" s="3"/>
       <c r="F33" s="3"/>
@@ -2799,7 +2799,7 @@
         <v>1</v>
       </c>
       <c r="M33" s="7" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="N33" s="8">
         <v>44384</v>
@@ -2818,19 +2818,19 @@
         <v>53</v>
       </c>
       <c r="B34" s="28" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="C34">
         <v>68</v>
       </c>
       <c r="D34" s="3" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E34" s="3" t="s">
+        <v>180</v>
+      </c>
+      <c r="F34" s="3" t="s">
         <v>181</v>
-      </c>
-      <c r="F34" s="3" t="s">
-        <v>182</v>
       </c>
       <c r="G34" s="8">
         <v>44401</v>
@@ -2851,7 +2851,7 @@
         <v>2</v>
       </c>
       <c r="M34" s="9" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="N34" s="8">
         <v>44373</v>
@@ -2870,19 +2870,19 @@
         <v>8</v>
       </c>
       <c r="B35" s="28" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="C35">
         <v>38</v>
       </c>
       <c r="D35" s="3" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E35" s="3" t="s">
+        <v>175</v>
+      </c>
+      <c r="F35" s="3" t="s">
         <v>176</v>
-      </c>
-      <c r="F35" s="3" t="s">
-        <v>177</v>
       </c>
       <c r="G35" s="8">
         <v>44394</v>
@@ -2920,19 +2920,19 @@
         <v>55</v>
       </c>
       <c r="B36" s="28" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="C36">
         <v>34</v>
       </c>
       <c r="D36" s="3" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E36" s="3" t="s">
+        <v>175</v>
+      </c>
+      <c r="F36" s="3" t="s">
         <v>176</v>
-      </c>
-      <c r="F36" s="3" t="s">
-        <v>177</v>
       </c>
       <c r="G36" s="8">
         <v>44399</v>
@@ -2953,7 +2953,7 @@
         <v>2</v>
       </c>
       <c r="M36" s="9" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="N36" s="8">
         <v>44372</v>
@@ -2972,19 +2972,19 @@
         <v>27</v>
       </c>
       <c r="B37" s="28" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="C37">
         <v>33</v>
       </c>
       <c r="D37" s="3" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E37" s="3" t="s">
+        <v>184</v>
+      </c>
+      <c r="F37" s="3" t="s">
         <v>185</v>
-      </c>
-      <c r="F37" s="3" t="s">
-        <v>186</v>
       </c>
       <c r="G37" s="8">
         <v>44403</v>
@@ -3005,7 +3005,7 @@
         <v>2</v>
       </c>
       <c r="M37" s="9" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="N37" s="8">
         <v>44369</v>
@@ -3016,19 +3016,19 @@
         <v>38</v>
       </c>
       <c r="B38" s="28" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="C38">
         <v>31</v>
       </c>
       <c r="D38" s="3" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E38" s="3" t="s">
+        <v>175</v>
+      </c>
+      <c r="F38" s="3" t="s">
         <v>176</v>
-      </c>
-      <c r="F38" s="3" t="s">
-        <v>177</v>
       </c>
       <c r="G38" s="8">
         <v>44404</v>
@@ -3049,7 +3049,7 @@
         <v>2</v>
       </c>
       <c r="M38" s="9" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="N38" s="8">
         <v>44368</v>
@@ -3068,19 +3068,19 @@
         <v>1</v>
       </c>
       <c r="B39" s="28" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="C39">
         <v>36</v>
       </c>
       <c r="D39" s="3" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E39" s="3" t="s">
+        <v>171</v>
+      </c>
+      <c r="F39" s="3" t="s">
         <v>172</v>
-      </c>
-      <c r="F39" s="3" t="s">
-        <v>173</v>
       </c>
       <c r="G39" s="8">
         <v>44400</v>
@@ -3101,7 +3101,7 @@
         <v>2</v>
       </c>
       <c r="M39" s="9" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="N39" s="8">
         <v>44363</v>
@@ -3112,19 +3112,19 @@
         <v>97</v>
       </c>
       <c r="B40" s="28" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="C40">
         <v>36</v>
       </c>
       <c r="D40" s="3" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E40" s="3" t="s">
+        <v>175</v>
+      </c>
+      <c r="F40" s="3" t="s">
         <v>176</v>
-      </c>
-      <c r="F40" s="3" t="s">
-        <v>177</v>
       </c>
       <c r="G40" s="8"/>
       <c r="H40" s="8"/>
@@ -3141,7 +3141,7 @@
         <v>1</v>
       </c>
       <c r="M40" s="9" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="N40" s="8">
         <v>44373</v>
@@ -3152,19 +3152,19 @@
         <v>76</v>
       </c>
       <c r="B41" s="28" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="C41">
         <v>57</v>
       </c>
       <c r="D41" s="3" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E41" s="3" t="s">
+        <v>175</v>
+      </c>
+      <c r="F41" s="3" t="s">
         <v>176</v>
-      </c>
-      <c r="F41" s="3" t="s">
-        <v>177</v>
       </c>
       <c r="G41" s="8">
         <v>44396</v>
@@ -3185,7 +3185,7 @@
         <v>2</v>
       </c>
       <c r="M41" s="9" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="N41" s="8">
         <v>44370</v>
@@ -3204,19 +3204,19 @@
         <v>49</v>
       </c>
       <c r="B42" s="28" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="C42">
         <v>58</v>
       </c>
       <c r="D42" s="3" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E42" s="3" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="F42" s="3" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="G42" s="8">
         <v>44394</v>
@@ -3237,7 +3237,7 @@
         <v>2</v>
       </c>
       <c r="M42" s="9" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="N42" s="8">
         <v>44367</v>
@@ -3256,19 +3256,19 @@
         <v>93</v>
       </c>
       <c r="B43" s="28" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="C43">
         <v>38</v>
       </c>
       <c r="D43" s="3" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E43" s="3" t="s">
+        <v>175</v>
+      </c>
+      <c r="F43" s="3" t="s">
         <v>176</v>
-      </c>
-      <c r="F43" s="3" t="s">
-        <v>177</v>
       </c>
       <c r="G43" s="8">
         <v>44405</v>
@@ -3289,7 +3289,7 @@
         <v>2</v>
       </c>
       <c r="M43" s="9" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="N43" s="8">
         <v>44371</v>
@@ -3308,19 +3308,19 @@
         <v>60</v>
       </c>
       <c r="B44" s="28" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="C44">
         <v>34</v>
       </c>
       <c r="D44" s="3" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E44" s="3" t="s">
+        <v>180</v>
+      </c>
+      <c r="F44" s="3" t="s">
         <v>181</v>
-      </c>
-      <c r="F44" s="3" t="s">
-        <v>182</v>
       </c>
       <c r="G44" s="8">
         <v>44401</v>
@@ -3341,7 +3341,7 @@
         <v>2</v>
       </c>
       <c r="M44" s="9" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="N44" s="8">
         <v>44368</v>
@@ -3360,19 +3360,19 @@
         <v>62</v>
       </c>
       <c r="B45" s="28" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="C45">
         <v>19</v>
       </c>
       <c r="D45" s="3" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E45" s="3" t="s">
+        <v>175</v>
+      </c>
+      <c r="F45" s="3" t="s">
         <v>176</v>
-      </c>
-      <c r="F45" s="3" t="s">
-        <v>177</v>
       </c>
       <c r="G45" s="8">
         <v>44400</v>
@@ -3393,7 +3393,7 @@
         <v>2</v>
       </c>
       <c r="M45" s="9" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="N45" s="8">
         <v>44368</v>
@@ -3416,7 +3416,7 @@
         <v>33</v>
       </c>
       <c r="D46" s="3" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E46" s="3"/>
       <c r="F46" s="3"/>
@@ -3435,7 +3435,7 @@
         <v>2</v>
       </c>
       <c r="M46" s="9" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="N46" s="8">
         <v>44376</v>
@@ -3446,19 +3446,19 @@
         <v>88</v>
       </c>
       <c r="B47" s="28" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="C47">
         <v>44</v>
       </c>
       <c r="D47" s="3" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E47" s="3" t="s">
+        <v>175</v>
+      </c>
+      <c r="F47" s="3" t="s">
         <v>176</v>
-      </c>
-      <c r="F47" s="3" t="s">
-        <v>177</v>
       </c>
       <c r="G47" s="8">
         <v>44394</v>
@@ -3479,7 +3479,7 @@
         <v>2</v>
       </c>
       <c r="M47" s="9" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="N47" s="8">
         <v>44368</v>
@@ -3498,19 +3498,19 @@
         <v>37</v>
       </c>
       <c r="B48" s="28" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="C48">
         <v>39</v>
       </c>
       <c r="D48" s="3" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E48" s="3" t="s">
+        <v>175</v>
+      </c>
+      <c r="F48" s="3" t="s">
         <v>176</v>
-      </c>
-      <c r="F48" s="3" t="s">
-        <v>177</v>
       </c>
       <c r="G48" s="8">
         <v>44404</v>
@@ -3531,7 +3531,7 @@
         <v>2</v>
       </c>
       <c r="M48" s="9" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="N48" s="8">
         <v>44363</v>
@@ -3542,19 +3542,19 @@
         <v>4</v>
       </c>
       <c r="B49" s="28" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="C49">
         <v>38</v>
       </c>
       <c r="D49" s="3" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E49" s="3" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="F49" s="3" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="G49" s="8">
         <v>44401</v>
@@ -3575,7 +3575,7 @@
         <v>2</v>
       </c>
       <c r="M49" s="9" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="N49" s="8">
         <v>44360</v>
@@ -3590,7 +3590,7 @@
         <v>57</v>
       </c>
       <c r="D50" s="3" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E50" s="3"/>
       <c r="F50" s="3"/>
@@ -3609,7 +3609,7 @@
         <v>1</v>
       </c>
       <c r="M50" s="7" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="N50" s="8">
         <v>44373</v>
@@ -3620,19 +3620,19 @@
         <v>16</v>
       </c>
       <c r="B51" s="28" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="C51">
         <v>46</v>
       </c>
       <c r="D51" s="3" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E51" s="3" t="s">
+        <v>184</v>
+      </c>
+      <c r="F51" s="3" t="s">
         <v>185</v>
-      </c>
-      <c r="F51" s="3" t="s">
-        <v>186</v>
       </c>
       <c r="G51" s="8">
         <v>44403</v>
@@ -3653,7 +3653,7 @@
         <v>2</v>
       </c>
       <c r="M51" s="9" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="N51" s="8">
         <v>44358</v>
@@ -3664,19 +3664,19 @@
         <v>19</v>
       </c>
       <c r="B52" s="28" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="C52">
         <v>45</v>
       </c>
       <c r="D52" s="3" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E52" s="3" t="s">
+        <v>175</v>
+      </c>
+      <c r="F52" s="3" t="s">
         <v>176</v>
-      </c>
-      <c r="F52" s="3" t="s">
-        <v>177</v>
       </c>
       <c r="G52" s="8">
         <v>44399</v>
@@ -3697,7 +3697,7 @@
         <v>2</v>
       </c>
       <c r="M52" s="9" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="N52" s="8">
         <v>44358</v>
@@ -3716,19 +3716,19 @@
         <v>98</v>
       </c>
       <c r="B53" s="28" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="C53">
         <v>30</v>
       </c>
       <c r="D53" s="3" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E53" s="3" t="s">
+        <v>175</v>
+      </c>
+      <c r="F53" s="3" t="s">
         <v>176</v>
-      </c>
-      <c r="F53" s="3" t="s">
-        <v>177</v>
       </c>
       <c r="G53" s="8"/>
       <c r="H53" s="8"/>
@@ -3745,7 +3745,7 @@
         <v>2</v>
       </c>
       <c r="M53" s="9" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="N53" s="8">
         <v>44365</v>
@@ -3764,19 +3764,19 @@
         <v>90</v>
       </c>
       <c r="B54" s="28" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="C54">
         <v>37</v>
       </c>
       <c r="D54" s="3" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E54" s="3" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="F54" s="3" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="G54" s="8">
         <v>44406</v>
@@ -3797,7 +3797,7 @@
         <v>2</v>
       </c>
       <c r="M54" s="9" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="N54" s="8">
         <v>44364</v>
@@ -3808,19 +3808,19 @@
         <v>26</v>
       </c>
       <c r="B55" s="28" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="C55">
         <v>50</v>
       </c>
       <c r="D55" s="3" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E55" s="3" t="s">
+        <v>175</v>
+      </c>
+      <c r="F55" s="3" t="s">
         <v>176</v>
-      </c>
-      <c r="F55" s="3" t="s">
-        <v>177</v>
       </c>
       <c r="G55" s="8">
         <v>44401</v>
@@ -3858,19 +3858,19 @@
         <v>10</v>
       </c>
       <c r="B56" s="28" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="C56">
         <v>37</v>
       </c>
       <c r="D56" s="3" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E56" s="3" t="s">
+        <v>178</v>
+      </c>
+      <c r="F56" s="3" t="s">
         <v>179</v>
-      </c>
-      <c r="F56" s="3" t="s">
-        <v>180</v>
       </c>
       <c r="G56" s="8">
         <v>44401</v>
@@ -3900,19 +3900,19 @@
         <v>18</v>
       </c>
       <c r="B57" s="28" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="C57">
         <v>33</v>
       </c>
       <c r="D57" s="3" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E57" s="3" t="s">
+        <v>175</v>
+      </c>
+      <c r="F57" s="3" t="s">
         <v>176</v>
-      </c>
-      <c r="F57" s="3" t="s">
-        <v>177</v>
       </c>
       <c r="G57" s="8">
         <v>44399</v>
@@ -3933,7 +3933,7 @@
         <v>2</v>
       </c>
       <c r="M57" s="9" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="N57" s="8">
         <v>44355</v>
@@ -3952,19 +3952,19 @@
         <v>58</v>
       </c>
       <c r="B58" s="28" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="C58">
         <v>28</v>
       </c>
       <c r="D58" s="3" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E58" s="3" t="s">
+        <v>178</v>
+      </c>
+      <c r="F58" s="3" t="s">
         <v>179</v>
-      </c>
-      <c r="F58" s="3" t="s">
-        <v>180</v>
       </c>
       <c r="G58" s="8">
         <v>44403</v>
@@ -3985,7 +3985,7 @@
         <v>2</v>
       </c>
       <c r="M58" s="9" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="N58" s="8">
         <v>44358</v>
@@ -4004,19 +4004,19 @@
         <v>28</v>
       </c>
       <c r="B59" s="28" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="C59">
         <v>39</v>
       </c>
       <c r="D59" s="3" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E59" s="3" t="s">
+        <v>175</v>
+      </c>
+      <c r="F59" s="3" t="s">
         <v>176</v>
-      </c>
-      <c r="F59" s="3" t="s">
-        <v>177</v>
       </c>
       <c r="G59" s="8">
         <v>44400</v>
@@ -4037,7 +4037,7 @@
         <v>2</v>
       </c>
       <c r="M59" s="9" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="N59" s="8">
         <v>44354</v>
@@ -4048,19 +4048,19 @@
         <v>50</v>
       </c>
       <c r="B60" s="28" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="C60">
         <v>20</v>
       </c>
       <c r="D60" s="3" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E60" s="3" t="s">
+        <v>175</v>
+      </c>
+      <c r="F60" s="3" t="s">
         <v>176</v>
-      </c>
-      <c r="F60" s="3" t="s">
-        <v>177</v>
       </c>
       <c r="G60" s="8">
         <v>44397</v>
@@ -4081,7 +4081,7 @@
         <v>2</v>
       </c>
       <c r="M60" s="9" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="N60" s="8">
         <v>44354</v>
@@ -4100,19 +4100,19 @@
         <v>71</v>
       </c>
       <c r="B61" s="28" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="C61">
         <v>52</v>
       </c>
       <c r="D61" s="3" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E61" s="3" t="s">
+        <v>175</v>
+      </c>
+      <c r="F61" s="3" t="s">
         <v>176</v>
-      </c>
-      <c r="F61" s="3" t="s">
-        <v>177</v>
       </c>
       <c r="G61" s="8">
         <v>44403</v>
@@ -4133,7 +4133,7 @@
         <v>2</v>
       </c>
       <c r="M61" s="9" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="N61" s="8">
         <v>44354</v>
@@ -4144,19 +4144,19 @@
         <v>110</v>
       </c>
       <c r="B62" s="28" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="C62">
         <v>52</v>
       </c>
       <c r="D62" s="3" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E62" s="3" t="s">
+        <v>175</v>
+      </c>
+      <c r="F62" s="3" t="s">
         <v>176</v>
-      </c>
-      <c r="F62" s="3" t="s">
-        <v>177</v>
       </c>
       <c r="G62" s="8"/>
       <c r="H62" s="8"/>
@@ -4173,7 +4173,7 @@
         <v>2</v>
       </c>
       <c r="M62" s="9" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="N62" s="8">
         <v>44359</v>
@@ -4192,19 +4192,19 @@
         <v>114</v>
       </c>
       <c r="B63" s="28" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="C63">
         <v>56</v>
       </c>
       <c r="D63" s="3" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E63" s="3" t="s">
+        <v>175</v>
+      </c>
+      <c r="F63" s="3" t="s">
         <v>176</v>
-      </c>
-      <c r="F63" s="3" t="s">
-        <v>177</v>
       </c>
       <c r="G63" s="8"/>
       <c r="H63" s="8"/>
@@ -4221,7 +4221,7 @@
         <v>2</v>
       </c>
       <c r="M63" s="9" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="N63" s="8">
         <v>44359</v>
@@ -4240,19 +4240,19 @@
         <v>108</v>
       </c>
       <c r="B64" s="28" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="C64">
         <v>37</v>
       </c>
       <c r="D64" s="3" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E64" s="3" t="s">
+        <v>175</v>
+      </c>
+      <c r="F64" s="3" t="s">
         <v>176</v>
-      </c>
-      <c r="F64" s="3" t="s">
-        <v>177</v>
       </c>
       <c r="G64" s="8"/>
       <c r="H64" s="8"/>
@@ -4269,7 +4269,7 @@
         <v>2</v>
       </c>
       <c r="M64" s="9" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="N64" s="8">
         <v>44358</v>
@@ -4288,19 +4288,19 @@
         <v>44</v>
       </c>
       <c r="B65" s="28" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="C65">
         <v>51</v>
       </c>
       <c r="D65" s="3" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E65" s="3" t="s">
+        <v>178</v>
+      </c>
+      <c r="F65" s="3" t="s">
         <v>179</v>
-      </c>
-      <c r="F65" s="3" t="s">
-        <v>180</v>
       </c>
       <c r="G65" s="8">
         <v>44391</v>
@@ -4330,19 +4330,19 @@
         <v>68</v>
       </c>
       <c r="B66" s="28" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="C66">
         <v>58</v>
       </c>
       <c r="D66" s="3" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E66" s="3" t="s">
+        <v>178</v>
+      </c>
+      <c r="F66" s="3" t="s">
         <v>179</v>
-      </c>
-      <c r="F66" s="3" t="s">
-        <v>180</v>
       </c>
       <c r="G66" s="8">
         <v>44403</v>
@@ -4380,19 +4380,19 @@
         <v>95</v>
       </c>
       <c r="B67" s="28" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="C67">
         <v>50</v>
       </c>
       <c r="D67" s="3" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E67" s="3" t="s">
+        <v>175</v>
+      </c>
+      <c r="F67" s="3" t="s">
         <v>176</v>
-      </c>
-      <c r="F67" s="3" t="s">
-        <v>177</v>
       </c>
       <c r="G67" s="8"/>
       <c r="H67" s="8"/>
@@ -4409,7 +4409,7 @@
         <v>2</v>
       </c>
       <c r="M67" s="9" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="N67" s="8">
         <v>44313</v>
@@ -4428,19 +4428,19 @@
         <v>96</v>
       </c>
       <c r="B68" s="28" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="C68">
         <v>56</v>
       </c>
       <c r="D68" s="3" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E68" s="3" t="s">
+        <v>175</v>
+      </c>
+      <c r="F68" s="3" t="s">
         <v>176</v>
-      </c>
-      <c r="F68" s="3" t="s">
-        <v>177</v>
       </c>
       <c r="G68" s="8"/>
       <c r="H68" s="8"/>
@@ -4457,7 +4457,7 @@
         <v>2</v>
       </c>
       <c r="M68" s="9" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="N68" s="8">
         <v>44281</v>
@@ -4476,19 +4476,19 @@
         <v>102</v>
       </c>
       <c r="B69" s="28" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="C69">
         <v>41</v>
       </c>
       <c r="D69" s="3" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E69" s="3" t="s">
+        <v>175</v>
+      </c>
+      <c r="F69" s="3" t="s">
         <v>176</v>
-      </c>
-      <c r="F69" s="3" t="s">
-        <v>177</v>
       </c>
       <c r="G69" s="8"/>
       <c r="H69" s="8"/>
@@ -4505,7 +4505,7 @@
         <v>2</v>
       </c>
       <c r="M69" s="9" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="N69" s="8">
         <v>44280</v>
@@ -4524,19 +4524,19 @@
         <v>103</v>
       </c>
       <c r="B70" s="28" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="C70">
         <v>35</v>
       </c>
       <c r="D70" s="3" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E70" s="3" t="s">
+        <v>175</v>
+      </c>
+      <c r="F70" s="3" t="s">
         <v>176</v>
-      </c>
-      <c r="F70" s="3" t="s">
-        <v>177</v>
       </c>
       <c r="G70" s="8"/>
       <c r="H70" s="8"/>
@@ -4553,7 +4553,7 @@
         <v>2</v>
       </c>
       <c r="M70" s="9" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="N70" s="8">
         <v>44247</v>
@@ -4572,19 +4572,19 @@
         <v>2</v>
       </c>
       <c r="B71" s="28" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="C71">
         <v>12</v>
       </c>
       <c r="D71" s="3" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E71" s="3" t="s">
+        <v>173</v>
+      </c>
+      <c r="F71" s="3" t="s">
         <v>174</v>
-      </c>
-      <c r="F71" s="3" t="s">
-        <v>175</v>
       </c>
       <c r="G71" s="8">
         <v>44401</v>
@@ -4612,19 +4612,19 @@
         <v>5</v>
       </c>
       <c r="B72" s="28" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="C72">
         <v>3</v>
       </c>
       <c r="D72" s="3" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E72" s="3" t="s">
+        <v>173</v>
+      </c>
+      <c r="F72" s="3" t="s">
         <v>174</v>
-      </c>
-      <c r="F72" s="3" t="s">
-        <v>175</v>
       </c>
       <c r="G72" s="8">
         <v>44401</v>
@@ -4652,19 +4652,19 @@
         <v>7</v>
       </c>
       <c r="B73" s="28" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="C73">
         <v>11</v>
       </c>
       <c r="D73" s="3" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E73" s="3" t="s">
+        <v>178</v>
+      </c>
+      <c r="F73" s="3" t="s">
         <v>179</v>
-      </c>
-      <c r="F73" s="3" t="s">
-        <v>180</v>
       </c>
       <c r="G73" s="8">
         <v>44401</v>
@@ -4700,19 +4700,19 @@
         <v>13</v>
       </c>
       <c r="B74" s="28" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="C74">
         <v>8</v>
       </c>
       <c r="D74" s="3" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E74" s="3" t="s">
+        <v>178</v>
+      </c>
+      <c r="F74" s="3" t="s">
         <v>179</v>
-      </c>
-      <c r="F74" s="3" t="s">
-        <v>180</v>
       </c>
       <c r="G74" s="8">
         <v>44401</v>
@@ -4740,19 +4740,19 @@
         <v>14</v>
       </c>
       <c r="B75" s="28" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="C75">
         <v>6</v>
       </c>
       <c r="D75" s="3" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E75" s="3" t="s">
+        <v>178</v>
+      </c>
+      <c r="F75" s="3" t="s">
         <v>179</v>
-      </c>
-      <c r="F75" s="3" t="s">
-        <v>180</v>
       </c>
       <c r="G75" s="8">
         <v>44401</v>
@@ -4780,19 +4780,19 @@
         <v>20</v>
       </c>
       <c r="B76" s="28" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="C76">
         <v>37</v>
       </c>
       <c r="D76" s="3" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E76" s="3" t="s">
+        <v>178</v>
+      </c>
+      <c r="F76" s="3" t="s">
         <v>179</v>
-      </c>
-      <c r="F76" s="3" t="s">
-        <v>180</v>
       </c>
       <c r="G76" s="8">
         <v>44403</v>
@@ -4828,19 +4828,19 @@
         <v>21</v>
       </c>
       <c r="B77" s="28" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="C77">
         <v>9</v>
       </c>
       <c r="D77" s="3" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E77" s="3" t="s">
+        <v>178</v>
+      </c>
+      <c r="F77" s="3" t="s">
         <v>179</v>
-      </c>
-      <c r="F77" s="3" t="s">
-        <v>180</v>
       </c>
       <c r="G77" s="8">
         <v>44402</v>
@@ -4876,19 +4876,19 @@
         <v>22</v>
       </c>
       <c r="B78" s="28" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="C78">
         <v>8</v>
       </c>
       <c r="D78" s="3" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E78" s="3" t="s">
+        <v>178</v>
+      </c>
+      <c r="F78" s="3" t="s">
         <v>179</v>
-      </c>
-      <c r="F78" s="3" t="s">
-        <v>180</v>
       </c>
       <c r="G78" s="8">
         <v>44401</v>
@@ -4916,19 +4916,19 @@
         <v>23</v>
       </c>
       <c r="B79" s="28" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="C79">
         <v>14</v>
       </c>
       <c r="D79" s="3" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E79" s="3" t="s">
+        <v>178</v>
+      </c>
+      <c r="F79" s="3" t="s">
         <v>179</v>
-      </c>
-      <c r="F79" s="3" t="s">
-        <v>180</v>
       </c>
       <c r="G79" s="8">
         <v>44402</v>
@@ -4964,19 +4964,19 @@
         <v>24</v>
       </c>
       <c r="B80" s="28" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="C80">
         <v>40</v>
       </c>
       <c r="D80" s="3" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E80" s="3" t="s">
+        <v>178</v>
+      </c>
+      <c r="F80" s="3" t="s">
         <v>179</v>
-      </c>
-      <c r="F80" s="3" t="s">
-        <v>180</v>
       </c>
       <c r="G80" s="8">
         <v>44402</v>
@@ -5012,19 +5012,19 @@
         <v>29</v>
       </c>
       <c r="B81" s="28" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="C81">
         <v>9</v>
       </c>
       <c r="D81" s="3" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E81" s="3" t="s">
+        <v>175</v>
+      </c>
+      <c r="F81" s="3" t="s">
         <v>176</v>
-      </c>
-      <c r="F81" s="3" t="s">
-        <v>177</v>
       </c>
       <c r="G81" s="8">
         <v>44406</v>
@@ -5052,19 +5052,19 @@
         <v>30</v>
       </c>
       <c r="B82" s="28" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="C82">
         <v>8</v>
       </c>
       <c r="D82" s="3" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E82" s="3" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="F82" s="3" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="G82" s="8">
         <v>44401</v>
@@ -5092,19 +5092,19 @@
         <v>31</v>
       </c>
       <c r="B83" s="28" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="C83">
         <v>3</v>
       </c>
       <c r="D83" s="3" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E83" s="3" t="s">
+        <v>182</v>
+      </c>
+      <c r="F83" s="3" t="s">
         <v>183</v>
-      </c>
-      <c r="F83" s="3" t="s">
-        <v>184</v>
       </c>
       <c r="G83" s="8">
         <v>44401</v>
@@ -5132,19 +5132,19 @@
         <v>32</v>
       </c>
       <c r="B84" s="28" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="C84">
         <v>65</v>
       </c>
       <c r="D84" s="3" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E84" s="3" t="s">
+        <v>180</v>
+      </c>
+      <c r="F84" s="3" t="s">
         <v>181</v>
-      </c>
-      <c r="F84" s="3" t="s">
-        <v>182</v>
       </c>
       <c r="G84" s="8">
         <v>44400</v>
@@ -5180,19 +5180,19 @@
         <v>33</v>
       </c>
       <c r="B85" s="28" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="C85">
         <v>61</v>
       </c>
       <c r="D85" s="3" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E85" s="3" t="s">
+        <v>180</v>
+      </c>
+      <c r="F85" s="3" t="s">
         <v>181</v>
-      </c>
-      <c r="F85" s="3" t="s">
-        <v>182</v>
       </c>
       <c r="G85" s="8">
         <v>44400</v>
@@ -5228,19 +5228,19 @@
         <v>34</v>
       </c>
       <c r="B86" s="28" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="C86">
         <v>9</v>
       </c>
       <c r="D86" s="3" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E86" s="3" t="s">
+        <v>180</v>
+      </c>
+      <c r="F86" s="3" t="s">
         <v>181</v>
-      </c>
-      <c r="F86" s="3" t="s">
-        <v>182</v>
       </c>
       <c r="G86" s="8">
         <v>44398</v>
@@ -5276,19 +5276,19 @@
         <v>35</v>
       </c>
       <c r="B87" s="28" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="C87">
         <v>69</v>
       </c>
       <c r="D87" s="3" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E87" s="3" t="s">
+        <v>180</v>
+      </c>
+      <c r="F87" s="3" t="s">
         <v>181</v>
-      </c>
-      <c r="F87" s="3" t="s">
-        <v>182</v>
       </c>
       <c r="G87" s="8">
         <v>44400</v>
@@ -5324,19 +5324,19 @@
         <v>39</v>
       </c>
       <c r="B88" s="28" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="C88">
         <v>7</v>
       </c>
       <c r="D88" s="3" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E88" s="3" t="s">
+        <v>175</v>
+      </c>
+      <c r="F88" s="3" t="s">
         <v>176</v>
-      </c>
-      <c r="F88" s="3" t="s">
-        <v>177</v>
       </c>
       <c r="G88" s="8">
         <v>44400</v>
@@ -5364,19 +5364,19 @@
         <v>41</v>
       </c>
       <c r="B89" s="28" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="C89">
         <v>32</v>
       </c>
       <c r="D89" s="3" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E89" s="3" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="F89" s="3" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="G89" s="8">
         <v>44403</v>
@@ -5412,19 +5412,19 @@
         <v>42</v>
       </c>
       <c r="B90" s="28" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="C90">
         <v>34</v>
       </c>
       <c r="D90" s="3" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E90" s="3" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="F90" s="3" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="G90" s="8">
         <v>44403</v>
@@ -5460,19 +5460,19 @@
         <v>43</v>
       </c>
       <c r="B91" s="28" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="C91">
         <v>9</v>
       </c>
       <c r="D91" s="3" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E91" s="3" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="F91" s="3" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="G91" s="8">
         <v>44403</v>
@@ -5508,19 +5508,19 @@
         <v>45</v>
       </c>
       <c r="B92" s="28" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="C92">
         <v>17</v>
       </c>
       <c r="D92" s="3" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E92" s="3" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="F92" s="3" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="G92" s="8">
         <v>44402</v>
@@ -5556,19 +5556,19 @@
         <v>48</v>
       </c>
       <c r="B93" s="28" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="C93">
         <v>4</v>
       </c>
       <c r="D93" s="3" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E93" s="3" t="s">
+        <v>178</v>
+      </c>
+      <c r="F93" s="3" t="s">
         <v>179</v>
-      </c>
-      <c r="F93" s="3" t="s">
-        <v>180</v>
       </c>
       <c r="G93" s="8">
         <v>44403</v>
@@ -5604,19 +5604,19 @@
         <v>52</v>
       </c>
       <c r="B94" s="28" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="C94">
         <v>7</v>
       </c>
       <c r="D94" s="3" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E94" s="3" t="s">
+        <v>175</v>
+      </c>
+      <c r="F94" s="3" t="s">
         <v>176</v>
-      </c>
-      <c r="F94" s="3" t="s">
-        <v>177</v>
       </c>
       <c r="G94" s="8">
         <v>44404</v>
@@ -5652,19 +5652,19 @@
         <v>56</v>
       </c>
       <c r="B95" s="28" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="C95">
         <v>9</v>
       </c>
       <c r="D95" s="3" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E95" s="3" t="s">
+        <v>175</v>
+      </c>
+      <c r="F95" s="3" t="s">
         <v>176</v>
-      </c>
-      <c r="F95" s="3" t="s">
-        <v>177</v>
       </c>
       <c r="G95" s="8">
         <v>44397</v>
@@ -5700,19 +5700,19 @@
         <v>59</v>
       </c>
       <c r="B96" s="28" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="C96">
         <v>13</v>
       </c>
       <c r="D96" s="3" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E96" s="3" t="s">
+        <v>182</v>
+      </c>
+      <c r="F96" s="3" t="s">
         <v>183</v>
-      </c>
-      <c r="F96" s="3" t="s">
-        <v>184</v>
       </c>
       <c r="G96" s="8">
         <v>44401</v>
@@ -5740,19 +5740,19 @@
         <v>61</v>
       </c>
       <c r="B97" s="28" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="C97">
         <v>60</v>
       </c>
       <c r="D97" s="3" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E97" s="3" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="F97" s="3" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="G97" s="8">
         <v>44394</v>
@@ -5788,19 +5788,19 @@
         <v>63</v>
       </c>
       <c r="B98" s="28" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="C98">
         <v>16</v>
       </c>
       <c r="D98" s="3" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E98" s="3" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="F98" s="3" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="G98" s="8">
         <v>44405</v>
@@ -5836,19 +5836,19 @@
         <v>64</v>
       </c>
       <c r="B99" s="28" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="C99">
         <v>15</v>
       </c>
       <c r="D99" s="3" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E99" s="3" t="s">
+        <v>175</v>
+      </c>
+      <c r="F99" s="3" t="s">
         <v>176</v>
-      </c>
-      <c r="F99" s="3" t="s">
-        <v>177</v>
       </c>
       <c r="G99" s="8">
         <v>44405</v>
@@ -5884,19 +5884,19 @@
         <v>65</v>
       </c>
       <c r="B100" s="28" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="C100">
         <v>42</v>
       </c>
       <c r="D100" s="3" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E100" s="3" t="s">
+        <v>175</v>
+      </c>
+      <c r="F100" s="3" t="s">
         <v>176</v>
-      </c>
-      <c r="F100" s="3" t="s">
-        <v>177</v>
       </c>
       <c r="G100" s="8">
         <v>44401</v>
@@ -5932,19 +5932,19 @@
         <v>66</v>
       </c>
       <c r="B101" s="28" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="C101">
         <v>15</v>
       </c>
       <c r="D101" s="3" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E101" s="3" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="F101" s="3" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="G101" s="8">
         <v>44403</v>
@@ -5980,19 +5980,19 @@
         <v>70</v>
       </c>
       <c r="B102" s="28" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="C102">
         <v>17</v>
       </c>
       <c r="D102" s="3" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E102" s="3" t="s">
+        <v>175</v>
+      </c>
+      <c r="F102" s="3" t="s">
         <v>176</v>
-      </c>
-      <c r="F102" s="3" t="s">
-        <v>177</v>
       </c>
       <c r="G102" s="8"/>
       <c r="H102" s="8"/>
@@ -6016,19 +6016,19 @@
         <v>72</v>
       </c>
       <c r="B103" s="28" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="C103">
         <v>8</v>
       </c>
       <c r="D103" s="3" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E103" s="3" t="s">
+        <v>175</v>
+      </c>
+      <c r="F103" s="3" t="s">
         <v>176</v>
-      </c>
-      <c r="F103" s="3" t="s">
-        <v>177</v>
       </c>
       <c r="G103" s="8">
         <v>44403</v>
@@ -6064,19 +6064,19 @@
         <v>74</v>
       </c>
       <c r="B104" s="28" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="C104">
         <v>64</v>
       </c>
       <c r="D104" s="3" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E104" s="3" t="s">
+        <v>178</v>
+      </c>
+      <c r="F104" s="3" t="s">
         <v>179</v>
-      </c>
-      <c r="F104" s="3" t="s">
-        <v>180</v>
       </c>
       <c r="G104" s="8">
         <v>44402</v>
@@ -6112,19 +6112,19 @@
         <v>75</v>
       </c>
       <c r="B105" s="28" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="C105">
         <v>11</v>
       </c>
       <c r="D105" s="3" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E105" s="3" t="s">
+        <v>178</v>
+      </c>
+      <c r="F105" s="3" t="s">
         <v>179</v>
-      </c>
-      <c r="F105" s="3" t="s">
-        <v>180</v>
       </c>
       <c r="G105" s="8">
         <v>44403</v>
@@ -6160,19 +6160,19 @@
         <v>78</v>
       </c>
       <c r="B106" s="28" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="C106">
         <v>70</v>
       </c>
       <c r="D106" s="3" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E106" s="3" t="s">
+        <v>175</v>
+      </c>
+      <c r="F106" s="3" t="s">
         <v>176</v>
-      </c>
-      <c r="F106" s="3" t="s">
-        <v>177</v>
       </c>
       <c r="G106" s="8">
         <v>44406</v>
@@ -6208,19 +6208,19 @@
         <v>80</v>
       </c>
       <c r="B107" s="28" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="C107">
         <v>15</v>
       </c>
       <c r="D107" s="3" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E107" s="3" t="s">
+        <v>175</v>
+      </c>
+      <c r="F107" s="3" t="s">
         <v>176</v>
-      </c>
-      <c r="F107" s="3" t="s">
-        <v>177</v>
       </c>
       <c r="G107" s="8">
         <v>44406</v>
@@ -6256,19 +6256,19 @@
         <v>81</v>
       </c>
       <c r="B108" s="28" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="C108">
         <v>49</v>
       </c>
       <c r="D108" s="3" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E108" s="3" t="s">
+        <v>178</v>
+      </c>
+      <c r="F108" s="3" t="s">
         <v>179</v>
-      </c>
-      <c r="F108" s="3" t="s">
-        <v>180</v>
       </c>
       <c r="G108" s="8">
         <v>44406</v>
@@ -6304,19 +6304,19 @@
         <v>84</v>
       </c>
       <c r="B109" s="28" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="C109">
         <v>8</v>
       </c>
       <c r="D109" s="3" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E109" s="3" t="s">
+        <v>175</v>
+      </c>
+      <c r="F109" s="3" t="s">
         <v>176</v>
-      </c>
-      <c r="F109" s="3" t="s">
-        <v>177</v>
       </c>
       <c r="G109" s="8">
         <v>44402</v>
@@ -6352,19 +6352,19 @@
         <v>85</v>
       </c>
       <c r="B110" s="28" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="C110">
         <v>11</v>
       </c>
       <c r="D110" s="3" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E110" s="3" t="s">
+        <v>178</v>
+      </c>
+      <c r="F110" s="3" t="s">
         <v>179</v>
-      </c>
-      <c r="F110" s="3" t="s">
-        <v>180</v>
       </c>
       <c r="G110" s="8">
         <v>44403</v>
@@ -6400,19 +6400,19 @@
         <v>86</v>
       </c>
       <c r="B111" s="28" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="C111">
         <v>12</v>
       </c>
       <c r="D111" s="3" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E111" s="3" t="s">
+        <v>175</v>
+      </c>
+      <c r="F111" s="3" t="s">
         <v>176</v>
-      </c>
-      <c r="F111" s="3" t="s">
-        <v>177</v>
       </c>
       <c r="G111" s="8">
         <v>44399</v>
@@ -6448,19 +6448,19 @@
         <v>89</v>
       </c>
       <c r="B112" s="28" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="C112">
         <v>32</v>
       </c>
       <c r="D112" s="3" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E112" s="3" t="s">
+        <v>175</v>
+      </c>
+      <c r="F112" s="3" t="s">
         <v>176</v>
-      </c>
-      <c r="F112" s="3" t="s">
-        <v>177</v>
       </c>
       <c r="G112" s="8">
         <v>44405</v>
@@ -6496,19 +6496,19 @@
         <v>91</v>
       </c>
       <c r="B113" s="28" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="C113">
         <v>12</v>
       </c>
       <c r="D113" s="3" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E113" s="3" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="F113" s="3" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="G113" s="8">
         <v>44406</v>
@@ -6544,19 +6544,19 @@
         <v>92</v>
       </c>
       <c r="B114" s="28" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="C114">
         <v>34</v>
       </c>
       <c r="D114" s="3" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E114" s="3" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="F114" s="3" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="G114" s="8">
         <v>44404</v>
@@ -6592,19 +6592,19 @@
         <v>99</v>
       </c>
       <c r="B115" s="28" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="C115">
         <v>4</v>
       </c>
       <c r="D115" s="3" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E115" s="3" t="s">
+        <v>175</v>
+      </c>
+      <c r="F115" s="3" t="s">
         <v>176</v>
-      </c>
-      <c r="F115" s="3" t="s">
-        <v>177</v>
       </c>
       <c r="G115" s="8"/>
       <c r="H115" s="8"/>
@@ -6636,19 +6636,19 @@
         <v>100</v>
       </c>
       <c r="B116" s="28" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="C116">
         <v>63</v>
       </c>
       <c r="D116" s="3" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E116" s="3" t="s">
+        <v>175</v>
+      </c>
+      <c r="F116" s="3" t="s">
         <v>176</v>
-      </c>
-      <c r="F116" s="3" t="s">
-        <v>177</v>
       </c>
       <c r="G116" s="8"/>
       <c r="H116" s="8"/>
@@ -6680,19 +6680,19 @@
         <v>101</v>
       </c>
       <c r="B117" s="28" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="C117">
         <v>7</v>
       </c>
       <c r="D117" s="3" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E117" s="3" t="s">
+        <v>175</v>
+      </c>
+      <c r="F117" s="3" t="s">
         <v>176</v>
-      </c>
-      <c r="F117" s="3" t="s">
-        <v>177</v>
       </c>
       <c r="G117" s="8"/>
       <c r="H117" s="8"/>
@@ -6716,19 +6716,19 @@
         <v>104</v>
       </c>
       <c r="B118" s="28" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="C118">
         <v>36</v>
       </c>
       <c r="D118" s="3" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E118" s="3" t="s">
+        <v>175</v>
+      </c>
+      <c r="F118" s="3" t="s">
         <v>176</v>
-      </c>
-      <c r="F118" s="3" t="s">
-        <v>177</v>
       </c>
       <c r="G118" s="8"/>
       <c r="H118" s="8"/>
@@ -6760,19 +6760,19 @@
         <v>105</v>
       </c>
       <c r="B119" s="28" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="C119">
         <v>14</v>
       </c>
       <c r="D119" s="3" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E119" s="3" t="s">
+        <v>175</v>
+      </c>
+      <c r="F119" s="3" t="s">
         <v>176</v>
-      </c>
-      <c r="F119" s="3" t="s">
-        <v>177</v>
       </c>
       <c r="G119" s="8"/>
       <c r="H119" s="8"/>
@@ -6804,19 +6804,19 @@
         <v>106</v>
       </c>
       <c r="B120" s="28" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="C120">
         <v>40</v>
       </c>
       <c r="D120" s="3" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E120" s="3" t="s">
+        <v>175</v>
+      </c>
+      <c r="F120" s="3" t="s">
         <v>176</v>
-      </c>
-      <c r="F120" s="3" t="s">
-        <v>177</v>
       </c>
       <c r="G120" s="8"/>
       <c r="H120" s="8"/>
@@ -6848,19 +6848,19 @@
         <v>109</v>
       </c>
       <c r="B121" s="28" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="C121">
         <v>58</v>
       </c>
       <c r="D121" s="3" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E121" s="3" t="s">
+        <v>175</v>
+      </c>
+      <c r="F121" s="3" t="s">
         <v>176</v>
-      </c>
-      <c r="F121" s="3" t="s">
-        <v>177</v>
       </c>
       <c r="G121" s="8"/>
       <c r="H121" s="8"/>
@@ -6892,19 +6892,19 @@
         <v>111</v>
       </c>
       <c r="B122" s="28" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="C122">
         <v>11</v>
       </c>
       <c r="D122" s="3" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E122" s="3" t="s">
+        <v>175</v>
+      </c>
+      <c r="F122" s="3" t="s">
         <v>176</v>
-      </c>
-      <c r="F122" s="3" t="s">
-        <v>177</v>
       </c>
       <c r="G122" s="8"/>
       <c r="H122" s="8"/>
@@ -6936,19 +6936,19 @@
         <v>112</v>
       </c>
       <c r="B123" s="28" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="C123">
         <v>19</v>
       </c>
       <c r="D123" s="3" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E123" s="3" t="s">
+        <v>175</v>
+      </c>
+      <c r="F123" s="3" t="s">
         <v>176</v>
-      </c>
-      <c r="F123" s="3" t="s">
-        <v>177</v>
       </c>
       <c r="G123" s="8"/>
       <c r="H123" s="8"/>
@@ -6980,19 +6980,19 @@
         <v>115</v>
       </c>
       <c r="B124" s="28" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="C124">
         <v>17</v>
       </c>
       <c r="D124" s="3" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E124" s="3" t="s">
+        <v>175</v>
+      </c>
+      <c r="F124" s="3" t="s">
         <v>176</v>
-      </c>
-      <c r="F124" s="3" t="s">
-        <v>177</v>
       </c>
       <c r="G124" s="8"/>
       <c r="H124" s="8"/>
@@ -7024,19 +7024,19 @@
         <v>119</v>
       </c>
       <c r="B125" s="28" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="C125">
         <v>57</v>
       </c>
       <c r="D125" s="3" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E125" s="3" t="s">
+        <v>175</v>
+      </c>
+      <c r="F125" s="3" t="s">
         <v>176</v>
-      </c>
-      <c r="F125" s="3" t="s">
-        <v>177</v>
       </c>
       <c r="G125" s="8"/>
       <c r="H125" s="8"/>
@@ -7068,19 +7068,19 @@
         <v>122</v>
       </c>
       <c r="B126" s="28" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="C126">
         <v>63</v>
       </c>
       <c r="D126" s="3" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E126" s="3" t="s">
+        <v>175</v>
+      </c>
+      <c r="F126" s="3" t="s">
         <v>176</v>
-      </c>
-      <c r="F126" s="3" t="s">
-        <v>177</v>
       </c>
       <c r="G126" s="8"/>
       <c r="H126" s="8"/>
@@ -7112,19 +7112,19 @@
         <v>123</v>
       </c>
       <c r="B127" s="28" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="C127">
         <v>59</v>
       </c>
       <c r="D127" s="3" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E127" s="3" t="s">
+        <v>175</v>
+      </c>
+      <c r="F127" s="3" t="s">
         <v>176</v>
-      </c>
-      <c r="F127" s="3" t="s">
-        <v>177</v>
       </c>
       <c r="G127" s="8"/>
       <c r="H127" s="8"/>
@@ -7152,7 +7152,7 @@
         <v>13</v>
       </c>
       <c r="D128" s="3" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E128" s="3"/>
       <c r="F128" s="3"/>
@@ -7182,7 +7182,7 @@
         <v>12</v>
       </c>
       <c r="D129" s="3" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E129" s="3"/>
       <c r="F129" s="3"/>
@@ -7220,7 +7220,7 @@
         <v>8</v>
       </c>
       <c r="D130" s="3" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E130" s="3"/>
       <c r="F130" s="3"/>
@@ -7301,22 +7301,22 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B1" t="s">
         <v>11</v>
       </c>
-      <c r="B1" t="s">
-        <v>12</v>
-      </c>
       <c r="C1" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="E1" s="29" t="s">
+        <v>197</v>
+      </c>
+      <c r="F1" s="29" t="s">
         <v>198</v>
-      </c>
-      <c r="F1" s="29" t="s">
-        <v>199</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.2">
@@ -7324,7 +7324,7 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C2" s="7">
         <v>1</v>
@@ -7336,7 +7336,7 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C3" s="7">
         <v>2</v>
@@ -7348,13 +7348,13 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C4" s="7">
         <v>3</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.2">
@@ -7362,7 +7362,7 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C5" s="7">
         <v>4</v>
@@ -7374,7 +7374,7 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C6" s="7">
         <v>5</v>
@@ -7386,7 +7386,7 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C7" s="7">
         <v>6</v>
@@ -7404,7 +7404,7 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C8" s="7">
         <v>7</v>
@@ -7422,7 +7422,7 @@
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C9" s="7">
         <v>8</v>
@@ -7440,7 +7440,7 @@
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C10" s="7">
         <v>9</v>
@@ -7458,7 +7458,7 @@
         <v>10</v>
       </c>
       <c r="B11" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C11" s="7">
         <v>10</v>
@@ -7470,7 +7470,7 @@
         <v>11</v>
       </c>
       <c r="B12" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C12" s="7">
         <v>11</v>
@@ -7488,7 +7488,7 @@
         <v>12</v>
       </c>
       <c r="B13" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C13" s="7">
         <v>12</v>
@@ -7500,7 +7500,7 @@
         <v>13</v>
       </c>
       <c r="B14" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C14" s="7">
         <v>13</v>
@@ -7512,7 +7512,7 @@
         <v>14</v>
       </c>
       <c r="B15" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C15" s="7">
         <v>14</v>
@@ -7524,7 +7524,7 @@
         <v>15</v>
       </c>
       <c r="B16" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C16" s="7">
         <v>15</v>
@@ -7536,7 +7536,7 @@
         <v>16</v>
       </c>
       <c r="B17" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C17" s="7">
         <v>16</v>
@@ -7548,13 +7548,13 @@
         <v>17</v>
       </c>
       <c r="B18" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C18" s="7">
         <v>17</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E18" s="31">
         <v>20.05</v>
@@ -7568,13 +7568,13 @@
         <v>18</v>
       </c>
       <c r="B19" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C19" s="7">
         <v>18</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E19" s="31">
         <v>23.55</v>
@@ -7588,13 +7588,13 @@
         <v>19</v>
       </c>
       <c r="B20" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C20" s="7">
         <v>19</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E20" s="31">
         <v>36.06</v>
@@ -7608,13 +7608,13 @@
         <v>20</v>
       </c>
       <c r="B21" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C21" s="7">
         <v>20</v>
       </c>
       <c r="D21" s="20" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E21">
         <v>35.9</v>
@@ -7628,13 +7628,13 @@
         <v>21</v>
       </c>
       <c r="B22" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C22" s="7">
         <v>21</v>
       </c>
       <c r="D22" s="7" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E22">
         <v>27.3</v>
@@ -7648,7 +7648,7 @@
         <v>22</v>
       </c>
       <c r="B23" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C23" s="7">
         <v>22</v>
@@ -7660,13 +7660,13 @@
         <v>23</v>
       </c>
       <c r="B24" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C24" s="7">
         <v>23</v>
       </c>
       <c r="D24" s="14" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E24">
         <v>30.5</v>
@@ -7680,13 +7680,13 @@
         <v>24</v>
       </c>
       <c r="B25" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C25" s="7">
         <v>24</v>
       </c>
       <c r="D25" s="20" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E25">
         <v>31.3</v>
@@ -7700,13 +7700,13 @@
         <v>25</v>
       </c>
       <c r="B26" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C26" s="7">
         <v>25</v>
       </c>
       <c r="D26" s="7" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.2">
@@ -7714,13 +7714,13 @@
         <v>26</v>
       </c>
       <c r="B27" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C27" s="7">
         <v>26</v>
       </c>
       <c r="D27" s="3" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E27" s="31">
         <v>22.9</v>
@@ -7734,7 +7734,7 @@
         <v>27</v>
       </c>
       <c r="B28" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C28" s="7">
         <v>27</v>
@@ -7746,13 +7746,13 @@
         <v>28</v>
       </c>
       <c r="B29" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C29" s="7">
         <v>28</v>
       </c>
       <c r="D29" s="3" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.2">
@@ -7760,13 +7760,13 @@
         <v>29</v>
       </c>
       <c r="B30" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C30" s="7">
         <v>29</v>
       </c>
       <c r="D30" s="3" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.2">
@@ -7774,7 +7774,7 @@
         <v>30</v>
       </c>
       <c r="B31" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C31" s="7">
         <v>30</v>
@@ -7786,7 +7786,7 @@
         <v>31</v>
       </c>
       <c r="B32" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C32" s="7">
         <v>31</v>
@@ -7798,7 +7798,7 @@
         <v>32</v>
       </c>
       <c r="B33" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C33" s="7">
         <v>32</v>
@@ -7816,7 +7816,7 @@
         <v>33</v>
       </c>
       <c r="B34" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C34" s="7">
         <v>33</v>
@@ -7834,7 +7834,7 @@
         <v>34</v>
       </c>
       <c r="B35" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C35" s="7">
         <v>34</v>
@@ -7852,7 +7852,7 @@
         <v>35</v>
       </c>
       <c r="B36" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C36" s="7">
         <v>35</v>
@@ -7870,7 +7870,7 @@
         <v>36</v>
       </c>
       <c r="B37" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C37" s="13">
         <v>36</v>
@@ -7882,13 +7882,13 @@
         <v>37</v>
       </c>
       <c r="B38" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C38" s="13">
         <v>37</v>
       </c>
       <c r="D38" s="3" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.2">
@@ -7896,13 +7896,13 @@
         <v>38</v>
       </c>
       <c r="B39" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C39" s="7">
         <v>38</v>
       </c>
       <c r="D39" s="3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E39" s="31">
         <v>23.62</v>
@@ -7916,13 +7916,13 @@
         <v>39</v>
       </c>
       <c r="B40" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C40" s="7">
         <v>39</v>
       </c>
       <c r="D40" s="3" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.2">
@@ -7930,13 +7930,13 @@
         <v>40</v>
       </c>
       <c r="B41" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C41" s="7">
         <v>40</v>
       </c>
       <c r="D41" s="14" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.2">
@@ -7944,13 +7944,13 @@
         <v>41</v>
       </c>
       <c r="B42" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C42" s="7">
         <v>41</v>
       </c>
       <c r="D42" s="3" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E42">
         <v>32.5</v>
@@ -7964,13 +7964,13 @@
         <v>42</v>
       </c>
       <c r="B43" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C43" s="7">
         <v>42</v>
       </c>
       <c r="D43" s="3" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E43">
         <v>25.9</v>
@@ -7984,13 +7984,13 @@
         <v>43</v>
       </c>
       <c r="B44" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C44" s="7">
         <v>43</v>
       </c>
       <c r="D44" s="3" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E44">
         <v>29.6</v>
@@ -8004,7 +8004,7 @@
         <v>44</v>
       </c>
       <c r="B45" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C45" s="7">
         <v>44</v>
@@ -8016,13 +8016,13 @@
         <v>45</v>
       </c>
       <c r="B46" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C46" s="7">
         <v>45</v>
       </c>
       <c r="D46" s="20" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="E46">
         <v>38.700000000000003</v>
@@ -8036,13 +8036,13 @@
         <v>46</v>
       </c>
       <c r="B47" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C47" s="7">
         <v>46</v>
       </c>
       <c r="D47" s="20" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E47">
         <v>30.1</v>
@@ -8056,7 +8056,7 @@
         <v>47</v>
       </c>
       <c r="B48" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C48" s="7">
         <v>47</v>
@@ -8068,13 +8068,13 @@
         <v>48</v>
       </c>
       <c r="B49" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C49" s="7">
         <v>48</v>
       </c>
       <c r="D49" s="14" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E49">
         <v>31.7</v>
@@ -8088,13 +8088,13 @@
         <v>49</v>
       </c>
       <c r="B50" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C50" s="7">
         <v>49</v>
       </c>
       <c r="D50" s="3" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E50" s="31">
         <v>33.31</v>
@@ -8108,13 +8108,13 @@
         <v>50</v>
       </c>
       <c r="B51" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C51" s="7">
         <v>50</v>
       </c>
       <c r="D51" s="3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E51">
         <v>16.28</v>
@@ -8128,13 +8128,13 @@
         <v>51</v>
       </c>
       <c r="B52" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C52" s="7">
         <v>51</v>
       </c>
       <c r="D52" s="3" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="E52" s="31">
         <v>28.45</v>
@@ -8148,13 +8148,13 @@
         <v>52</v>
       </c>
       <c r="B53" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C53" s="7">
         <v>52</v>
       </c>
       <c r="D53" s="3" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="E53" s="31">
         <v>36.33</v>
@@ -8168,7 +8168,7 @@
         <v>53</v>
       </c>
       <c r="B54" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C54" s="7">
         <v>53</v>
@@ -8186,7 +8186,7 @@
         <v>54</v>
       </c>
       <c r="B55" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C55" s="7">
         <v>54</v>
@@ -8204,13 +8204,13 @@
         <v>55</v>
       </c>
       <c r="B56" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C56" s="7">
         <v>55</v>
       </c>
       <c r="D56" s="3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E56" s="31">
         <v>19.3</v>
@@ -8224,13 +8224,13 @@
         <v>56</v>
       </c>
       <c r="B57" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C57" s="7">
         <v>56</v>
       </c>
       <c r="D57" s="3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E57" s="31">
         <v>38.299999999999997</v>
@@ -8244,13 +8244,13 @@
         <v>57</v>
       </c>
       <c r="B58" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C58" s="7">
         <v>57</v>
       </c>
       <c r="D58" s="3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.2">
@@ -8258,13 +8258,13 @@
         <v>58</v>
       </c>
       <c r="B59" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C59" s="7">
         <v>58</v>
       </c>
       <c r="D59" s="3" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E59">
         <v>37.799999999999997</v>
@@ -8278,7 +8278,7 @@
         <v>59</v>
       </c>
       <c r="B60" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C60" s="7">
         <v>59</v>
@@ -8290,7 +8290,7 @@
         <v>60</v>
       </c>
       <c r="B61" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C61" s="7">
         <v>60</v>
@@ -8308,13 +8308,13 @@
         <v>61</v>
       </c>
       <c r="B62" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C62" s="7">
         <v>61</v>
       </c>
       <c r="D62" s="3" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E62" s="31">
         <v>37.590000000000003</v>
@@ -8328,13 +8328,13 @@
         <v>62</v>
       </c>
       <c r="B63" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C63" s="7">
         <v>62</v>
       </c>
       <c r="D63" s="20" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E63" s="31">
         <v>25.14</v>
@@ -8348,13 +8348,13 @@
         <v>63</v>
       </c>
       <c r="B64" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C64" s="7">
         <v>63</v>
       </c>
       <c r="D64" s="3" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="E64" s="31">
         <v>12.37</v>
@@ -8368,13 +8368,13 @@
         <v>64</v>
       </c>
       <c r="B65" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C65" s="7">
         <v>64</v>
       </c>
       <c r="D65" s="3" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="E65" s="31">
         <v>23.19</v>
@@ -8388,13 +8388,13 @@
         <v>65</v>
       </c>
       <c r="B66" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="C66" s="7">
         <v>65</v>
       </c>
       <c r="D66" s="3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E66" s="31">
         <v>17.34</v>
@@ -8408,13 +8408,13 @@
         <v>66</v>
       </c>
       <c r="B67" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C67" s="7">
         <v>66</v>
       </c>
       <c r="D67" s="3" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E67">
         <v>37.799999999999997</v>
@@ -8428,13 +8428,13 @@
         <v>67</v>
       </c>
       <c r="B68" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C68" s="7">
         <v>67</v>
       </c>
       <c r="D68" s="20" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E68">
         <v>37.200000000000003</v>
@@ -8448,7 +8448,7 @@
         <v>68</v>
       </c>
       <c r="B69" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C69" s="7">
         <v>68</v>
@@ -8466,13 +8466,13 @@
         <v>69</v>
       </c>
       <c r="B70" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C70" s="7">
         <v>69</v>
       </c>
       <c r="D70" s="20" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E70">
         <v>27.8</v>
@@ -8486,13 +8486,13 @@
         <v>70</v>
       </c>
       <c r="B71" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C71" s="7">
         <v>70</v>
       </c>
       <c r="D71" s="3" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
     <row r="72" spans="1:6" x14ac:dyDescent="0.2">
@@ -8500,13 +8500,13 @@
         <v>71</v>
       </c>
       <c r="B72" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C72" s="7">
         <v>71</v>
       </c>
       <c r="D72" s="3" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
     </row>
     <row r="73" spans="1:6" x14ac:dyDescent="0.2">
@@ -8514,13 +8514,13 @@
         <v>72</v>
       </c>
       <c r="B73" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C73" s="7">
         <v>72</v>
       </c>
       <c r="D73" s="3" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="E73">
         <v>34.9</v>
@@ -8534,13 +8534,13 @@
         <v>73</v>
       </c>
       <c r="B74" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C74" s="7">
         <v>73</v>
       </c>
       <c r="D74" s="20" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E74">
         <v>27</v>
@@ -8554,13 +8554,13 @@
         <v>74</v>
       </c>
       <c r="B75" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C75" s="7">
         <v>74</v>
       </c>
       <c r="D75" s="3" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E75">
         <v>23.4</v>
@@ -8574,13 +8574,13 @@
         <v>75</v>
       </c>
       <c r="B76" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C76" s="7">
         <v>75</v>
       </c>
       <c r="D76" s="20" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E76">
         <v>31.01</v>
@@ -8594,13 +8594,13 @@
         <v>76</v>
       </c>
       <c r="B77" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C77" s="7">
         <v>76</v>
       </c>
       <c r="D77" s="3" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E77" s="31">
         <v>23.05</v>
@@ -8614,7 +8614,7 @@
         <v>77</v>
       </c>
       <c r="B78" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C78" s="7">
         <v>77</v>
@@ -8632,13 +8632,13 @@
         <v>78</v>
       </c>
       <c r="B79" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C79" s="7">
         <v>78</v>
       </c>
       <c r="D79" s="3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E79" s="31">
         <v>28.77</v>
@@ -8652,13 +8652,13 @@
         <v>79</v>
       </c>
       <c r="B80" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C80" s="7">
         <v>79</v>
       </c>
       <c r="D80" s="3" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="E80" s="31">
         <v>22.59</v>
@@ -8672,13 +8672,13 @@
         <v>80</v>
       </c>
       <c r="B81" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C81" s="7">
         <v>80</v>
       </c>
       <c r="D81" s="3" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="E81" s="31">
         <v>19.690000000000001</v>
@@ -8692,7 +8692,7 @@
         <v>81</v>
       </c>
       <c r="B82" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="C82" s="7">
         <v>81</v>
@@ -8710,13 +8710,13 @@
         <v>82</v>
       </c>
       <c r="B83" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C83" s="7">
         <v>82</v>
       </c>
       <c r="D83" s="3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E83" s="31">
         <v>24.73</v>
@@ -8730,13 +8730,13 @@
         <v>83</v>
       </c>
       <c r="B84" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C84" s="7">
         <v>83</v>
       </c>
       <c r="D84" s="3" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="E84" s="31">
         <v>16.27</v>
@@ -8750,13 +8750,13 @@
         <v>84</v>
       </c>
       <c r="B85" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C85" s="7">
         <v>84</v>
       </c>
       <c r="D85" s="3" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="E85" s="31">
         <v>30.55</v>
@@ -8770,13 +8770,13 @@
         <v>85</v>
       </c>
       <c r="B86" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="C86" s="7">
         <v>85</v>
       </c>
       <c r="D86" s="3" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E86">
         <v>38.76</v>
@@ -8790,13 +8790,13 @@
         <v>86</v>
       </c>
       <c r="B87" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="C87" s="7">
         <v>86</v>
       </c>
       <c r="D87" s="3" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="E87" s="31">
         <v>27.85</v>
@@ -8810,13 +8810,13 @@
         <v>87</v>
       </c>
       <c r="B88" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="C88" s="15">
         <v>87</v>
       </c>
       <c r="D88" s="3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E88" s="31">
         <v>18.48</v>
@@ -8830,13 +8830,13 @@
         <v>88</v>
       </c>
       <c r="B89" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C89" s="7">
         <v>88</v>
       </c>
       <c r="D89" s="3" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E89" s="31">
         <v>20.38</v>
@@ -8850,13 +8850,13 @@
         <v>89</v>
       </c>
       <c r="B90" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="C90" s="15">
         <v>89</v>
       </c>
       <c r="D90" s="3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E90" s="31">
         <v>16.399999999999999</v>
@@ -8870,13 +8870,13 @@
         <v>90</v>
       </c>
       <c r="B91" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="C91" s="7">
         <v>90</v>
       </c>
       <c r="D91" s="3" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
     </row>
     <row r="92" spans="1:6" x14ac:dyDescent="0.2">
@@ -8884,13 +8884,13 @@
         <v>91</v>
       </c>
       <c r="B92" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C92" s="7">
         <v>91</v>
       </c>
       <c r="D92" s="3" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="E92">
         <v>22.2</v>
@@ -8904,13 +8904,13 @@
         <v>92</v>
       </c>
       <c r="B93" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C93" s="7">
         <v>92</v>
       </c>
       <c r="D93" s="3" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E93">
         <v>22.41</v>
@@ -8924,13 +8924,13 @@
         <v>93</v>
       </c>
       <c r="B94" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="C94" s="15">
         <v>93</v>
       </c>
       <c r="D94" s="21" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="E94" s="31">
         <v>21.8</v>
@@ -8944,13 +8944,13 @@
         <v>94</v>
       </c>
       <c r="B95" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C95" s="7">
         <v>94</v>
       </c>
       <c r="D95" s="3" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="E95" s="31">
         <v>22.9</v>
@@ -8964,13 +8964,13 @@
         <v>95</v>
       </c>
       <c r="B96" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C96" s="7">
         <v>95</v>
       </c>
       <c r="D96" s="3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E96" s="31">
         <v>16.28</v>
@@ -8984,13 +8984,13 @@
         <v>96</v>
       </c>
       <c r="B97" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C97" s="7">
         <v>96</v>
       </c>
       <c r="D97" s="3" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="E97" s="31">
         <v>26.02</v>
@@ -9004,13 +9004,13 @@
         <v>97</v>
       </c>
       <c r="B98" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="C98" s="16">
         <v>97</v>
       </c>
       <c r="D98" s="22" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
     </row>
     <row r="99" spans="1:6" x14ac:dyDescent="0.2">
@@ -9018,13 +9018,13 @@
         <v>98</v>
       </c>
       <c r="B99" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C99" s="7">
         <v>98</v>
       </c>
       <c r="D99" s="3" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="E99" s="31">
         <v>25.88</v>
@@ -9038,13 +9038,13 @@
         <v>98</v>
       </c>
       <c r="B100" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C100" s="7">
         <v>98</v>
       </c>
       <c r="D100" s="3" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
     </row>
     <row r="101" spans="1:6" x14ac:dyDescent="0.2">
@@ -9052,13 +9052,13 @@
         <v>98</v>
       </c>
       <c r="B101" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C101" s="7">
         <v>98</v>
       </c>
       <c r="D101" s="3" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
     </row>
     <row r="102" spans="1:6" x14ac:dyDescent="0.2">
@@ -9066,13 +9066,13 @@
         <v>99</v>
       </c>
       <c r="B102" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="C102" s="7">
         <v>99</v>
       </c>
       <c r="D102" s="3" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="E102" s="31">
         <v>17.690000000000001</v>
@@ -9086,13 +9086,13 @@
         <v>100</v>
       </c>
       <c r="B103" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="C103" s="7">
         <v>100</v>
       </c>
       <c r="D103" s="3" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E103" s="31">
         <v>32.53</v>
@@ -9106,13 +9106,13 @@
         <v>101</v>
       </c>
       <c r="B104" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="C104" s="7">
         <v>101</v>
       </c>
       <c r="D104" s="23" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
     </row>
     <row r="105" spans="1:6" x14ac:dyDescent="0.2">
@@ -9120,13 +9120,13 @@
         <v>102</v>
       </c>
       <c r="B105" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="C105" s="7">
         <v>102</v>
       </c>
       <c r="D105" s="3" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="E105" s="31">
         <v>26.16</v>
@@ -9140,7 +9140,7 @@
         <v>103</v>
       </c>
       <c r="B106" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="C106" s="7">
         <v>103</v>
@@ -9158,13 +9158,13 @@
         <v>104</v>
       </c>
       <c r="B107" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="C107" s="7">
         <v>104</v>
       </c>
       <c r="D107" s="24" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="E107">
         <v>14.13</v>
@@ -9178,13 +9178,13 @@
         <v>104</v>
       </c>
       <c r="B108" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="C108" s="7">
         <v>104</v>
       </c>
       <c r="D108" s="24" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
     </row>
     <row r="109" spans="1:6" x14ac:dyDescent="0.2">
@@ -9192,13 +9192,13 @@
         <v>105</v>
       </c>
       <c r="B109" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="C109" s="7">
         <v>105</v>
       </c>
       <c r="D109" s="3" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="E109" s="31">
         <v>21.67</v>
@@ -9212,13 +9212,13 @@
         <v>106</v>
       </c>
       <c r="B110" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C110" s="7">
         <v>106</v>
       </c>
       <c r="D110" s="3" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="E110" s="31">
         <v>31.14</v>
@@ -9232,13 +9232,13 @@
         <v>107</v>
       </c>
       <c r="B111" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="C111" s="7">
         <v>107</v>
       </c>
       <c r="D111" s="3" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="E111" s="31">
         <v>27.39</v>
@@ -9252,13 +9252,13 @@
         <v>108</v>
       </c>
       <c r="B112" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="C112" s="7">
         <v>108</v>
       </c>
       <c r="D112" s="3" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="E112" s="31">
         <v>21.62</v>
@@ -9272,13 +9272,13 @@
         <v>109</v>
       </c>
       <c r="B113" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="C113" s="7">
         <v>109</v>
       </c>
       <c r="D113" s="3" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="E113" s="31">
         <v>25.92</v>
@@ -9292,13 +9292,13 @@
         <v>110</v>
       </c>
       <c r="B114" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="C114" s="7">
         <v>110</v>
       </c>
       <c r="D114" s="3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E114" s="31">
         <v>32.14</v>
@@ -9312,13 +9312,13 @@
         <v>111</v>
       </c>
       <c r="B115" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="C115" s="7">
         <v>111</v>
       </c>
       <c r="D115" s="3" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="E115" s="31">
         <v>21.11</v>
@@ -9332,13 +9332,13 @@
         <v>112</v>
       </c>
       <c r="B116" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="C116" s="7">
         <v>112</v>
       </c>
       <c r="D116" s="3" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="E116" s="31">
         <v>28.4</v>
@@ -9352,13 +9352,13 @@
         <v>113</v>
       </c>
       <c r="B117" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C117" s="7">
         <v>113</v>
       </c>
       <c r="D117" s="3" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="E117" s="31">
         <v>34.1</v>
@@ -9372,13 +9372,13 @@
         <v>114</v>
       </c>
       <c r="B118" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="C118" s="7">
         <v>114</v>
       </c>
       <c r="D118" s="3" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="E118" s="31">
         <v>27.19</v>
@@ -9392,13 +9392,13 @@
         <v>115</v>
       </c>
       <c r="B119" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="C119" s="16">
         <v>115</v>
       </c>
       <c r="D119" s="22" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="E119" s="31">
         <v>29.49</v>
@@ -9412,13 +9412,13 @@
         <v>116</v>
       </c>
       <c r="B120" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="C120" s="16">
         <v>116</v>
       </c>
       <c r="D120" s="22" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="E120" s="31">
         <v>32</v>
@@ -9432,13 +9432,13 @@
         <v>117</v>
       </c>
       <c r="B121" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="C121" s="16">
         <v>117</v>
       </c>
       <c r="D121" s="22" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E121" s="31">
         <v>37.54</v>
@@ -9452,13 +9452,13 @@
         <v>118</v>
       </c>
       <c r="B122" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="C122" s="16">
         <v>118</v>
       </c>
       <c r="D122" s="22" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="E122" s="31">
         <v>23</v>
@@ -9472,13 +9472,13 @@
         <v>119</v>
       </c>
       <c r="B123" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="C123" s="16">
         <v>119</v>
       </c>
       <c r="D123" s="22" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="E123" s="31">
         <v>14.67</v>
@@ -9492,13 +9492,13 @@
         <v>119</v>
       </c>
       <c r="B124" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="C124" s="16">
         <v>119</v>
       </c>
       <c r="D124" s="22" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
     </row>
     <row r="125" spans="1:6" x14ac:dyDescent="0.2">
@@ -9506,13 +9506,13 @@
         <v>120</v>
       </c>
       <c r="B125" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="C125" s="16">
         <v>120</v>
       </c>
       <c r="D125" s="16" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="E125" s="31">
         <v>13.88</v>
@@ -9526,13 +9526,13 @@
         <v>121</v>
       </c>
       <c r="B126" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="C126" s="16">
         <v>121</v>
       </c>
       <c r="D126" s="22" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E126" s="31">
         <v>20.58</v>
@@ -9546,13 +9546,13 @@
         <v>121</v>
       </c>
       <c r="B127" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="C127" s="16">
         <v>121</v>
       </c>
       <c r="D127" s="22" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
     </row>
     <row r="128" spans="1:6" x14ac:dyDescent="0.2">
@@ -9560,13 +9560,13 @@
         <v>122</v>
       </c>
       <c r="B128" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="C128" s="17">
         <v>122</v>
       </c>
       <c r="D128" s="25" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="E128" s="31">
         <v>23.8</v>
@@ -9580,13 +9580,13 @@
         <v>123</v>
       </c>
       <c r="B129" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="C129" s="17">
         <v>123</v>
       </c>
       <c r="D129" s="25" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
     </row>
     <row r="130" spans="1:6" x14ac:dyDescent="0.2">
@@ -9594,13 +9594,13 @@
         <v>123</v>
       </c>
       <c r="B130" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="C130" s="17">
         <v>123</v>
       </c>
       <c r="D130" s="25" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="E130" s="31">
         <v>36.9</v>
@@ -9614,7 +9614,7 @@
         <v>124</v>
       </c>
       <c r="B131" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="C131" s="18">
         <v>124</v>
@@ -9629,7 +9629,7 @@
         <v>125</v>
       </c>
       <c r="B132" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="C132" s="18">
         <v>125</v>
@@ -9641,13 +9641,13 @@
         <v>126</v>
       </c>
       <c r="B133" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="C133" s="18">
         <v>126</v>
       </c>
       <c r="D133" s="16" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="E133">
         <v>31.6</v>
@@ -9661,7 +9661,7 @@
         <v>127</v>
       </c>
       <c r="B134" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="C134" s="18">
         <v>127</v>
@@ -9673,13 +9673,13 @@
         <v>128</v>
       </c>
       <c r="B135" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="C135" s="18">
         <v>128</v>
       </c>
       <c r="D135" s="27" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="E135" s="31">
         <v>23.09</v>
@@ -9693,13 +9693,13 @@
         <v>129</v>
       </c>
       <c r="B136" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="C136" s="19">
         <v>129</v>
       </c>
       <c r="D136" s="16" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="E136" s="31">
         <v>31.31</v>
